--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/128.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/128.xlsx
@@ -426,13 +426,13 @@
         <v>-13.23065265695513</v>
       </c>
       <c r="E2">
-        <v>-28.72051257052458</v>
+        <v>-33.23444338391931</v>
       </c>
       <c r="F2">
-        <v>-3.4763524692254</v>
+        <v>-4.411667073930738</v>
       </c>
       <c r="G2">
-        <v>-16.65843787663874</v>
+        <v>-18.85468192702833</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.51999524395687</v>
       </c>
       <c r="E3">
-        <v>-28.91778195524672</v>
+        <v>-33.46925155392803</v>
       </c>
       <c r="F3">
-        <v>-3.396024025441126</v>
+        <v>-4.239595283551614</v>
       </c>
       <c r="G3">
-        <v>-16.54665068541417</v>
+        <v>-18.36351945918544</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.69585380527175</v>
       </c>
       <c r="E4">
-        <v>-28.95811707323304</v>
+        <v>-33.18014471633033</v>
       </c>
       <c r="F4">
-        <v>-3.461802195795226</v>
+        <v>-4.33772285771984</v>
       </c>
       <c r="G4">
-        <v>-16.09645290807422</v>
+        <v>-18.54259183322292</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.72525516251664</v>
       </c>
       <c r="E5">
-        <v>-29.55572167412926</v>
+        <v>-34.08362735831166</v>
       </c>
       <c r="F5">
-        <v>-3.398271386204921</v>
+        <v>-4.317326795528111</v>
       </c>
       <c r="G5">
-        <v>-16.2055353835932</v>
+        <v>-18.37854437011542</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.63022979904129</v>
       </c>
       <c r="E6">
-        <v>-29.56633641720324</v>
+        <v>-34.24905024957485</v>
       </c>
       <c r="F6">
-        <v>-3.454558122857745</v>
+        <v>-4.342170362305471</v>
       </c>
       <c r="G6">
-        <v>-15.68069473597931</v>
+        <v>-18.33514642864111</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.40062791295495</v>
       </c>
       <c r="E7">
-        <v>-30.22284740799125</v>
+        <v>-34.56590531165455</v>
       </c>
       <c r="F7">
-        <v>-3.602293307310023</v>
+        <v>-4.332079190604568</v>
       </c>
       <c r="G7">
-        <v>-15.36908798182264</v>
+        <v>-17.98319405599734</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.06191746357674</v>
       </c>
       <c r="E8">
-        <v>-30.10610561231051</v>
+        <v>-34.47445957178065</v>
       </c>
       <c r="F8">
-        <v>-3.573944918051418</v>
+        <v>-4.244388217344212</v>
       </c>
       <c r="G8">
-        <v>-15.371837389893</v>
+        <v>-17.54537937424704</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.62945425715674</v>
       </c>
       <c r="E9">
-        <v>-30.79897345666909</v>
+        <v>-34.99594052460794</v>
       </c>
       <c r="F9">
-        <v>-3.376153148182772</v>
+        <v>-4.393413169842648</v>
       </c>
       <c r="G9">
-        <v>-15.24304061568766</v>
+        <v>-17.54979067617812</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.10846450894875</v>
       </c>
       <c r="E10">
-        <v>-31.34908115793587</v>
+        <v>-35.59845172709148</v>
       </c>
       <c r="F10">
-        <v>-3.430616648182033</v>
+        <v>-4.302386361051219</v>
       </c>
       <c r="G10">
-        <v>-14.77692242484935</v>
+        <v>-17.29916251558205</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.53486060840421</v>
       </c>
       <c r="E11">
-        <v>-31.73730497037644</v>
+        <v>-35.83152322731826</v>
       </c>
       <c r="F11">
-        <v>-3.372690572439069</v>
+        <v>-4.363288760872441</v>
       </c>
       <c r="G11">
-        <v>-14.64575530003789</v>
+        <v>-17.18580612577187</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.93438393045566</v>
       </c>
       <c r="E12">
-        <v>-31.46105899896054</v>
+        <v>-36.17084857742401</v>
       </c>
       <c r="F12">
-        <v>-3.366199485470733</v>
+        <v>-4.227683360299357</v>
       </c>
       <c r="G12">
-        <v>-14.54170154319305</v>
+        <v>-17.04115349370618</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.32357160779486</v>
       </c>
       <c r="E13">
-        <v>-32.45032678830616</v>
+        <v>-36.59378087889637</v>
       </c>
       <c r="F13">
-        <v>-3.307085530872155</v>
+        <v>-4.251345675160325</v>
       </c>
       <c r="G13">
-        <v>-14.60318168440286</v>
+        <v>-16.78522183915621</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.74599391873377</v>
       </c>
       <c r="E14">
-        <v>-32.78029857534907</v>
+        <v>-37.4287816726967</v>
       </c>
       <c r="F14">
-        <v>-3.15389803217465</v>
+        <v>-4.230379696195469</v>
       </c>
       <c r="G14">
-        <v>-14.12250371428284</v>
+        <v>-16.44747501742145</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.216937592808488</v>
       </c>
       <c r="E15">
-        <v>-33.55460196778759</v>
+        <v>-37.73937611946079</v>
       </c>
       <c r="F15">
-        <v>-3.058378986957839</v>
+        <v>-4.127213991483416</v>
       </c>
       <c r="G15">
-        <v>-14.0176819108729</v>
+        <v>-16.09113617193815</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.745165350204802</v>
       </c>
       <c r="E16">
-        <v>-33.91895619373373</v>
+        <v>-38.27773469491466</v>
       </c>
       <c r="F16">
-        <v>-3.078578726075105</v>
+        <v>-3.968156681369674</v>
       </c>
       <c r="G16">
-        <v>-13.64465295005336</v>
+        <v>-16.06751211896991</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.345409846330025</v>
       </c>
       <c r="E17">
-        <v>-35.02030824324321</v>
+        <v>-38.74815710330547</v>
       </c>
       <c r="F17">
-        <v>-2.922308043904381</v>
+        <v>-3.871376860965803</v>
       </c>
       <c r="G17">
-        <v>-13.42727259830819</v>
+        <v>-16.0617285959128</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.001614777404223</v>
       </c>
       <c r="E18">
-        <v>-35.68079976268396</v>
+        <v>-39.07809039831931</v>
       </c>
       <c r="F18">
-        <v>-2.701099984293398</v>
+        <v>-3.778552494910298</v>
       </c>
       <c r="G18">
-        <v>-13.35942627802637</v>
+        <v>-15.75503800188195</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.703255826739128</v>
       </c>
       <c r="E19">
-        <v>-36.3294221517506</v>
+        <v>-39.82484934760618</v>
       </c>
       <c r="F19">
-        <v>-2.687972846061235</v>
+        <v>-3.610462666636431</v>
       </c>
       <c r="G19">
-        <v>-13.17687948644542</v>
+        <v>-15.67641751114257</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.441630063799696</v>
       </c>
       <c r="E20">
-        <v>-36.29450988138846</v>
+        <v>-40.64512127969656</v>
       </c>
       <c r="F20">
-        <v>-2.503515306275452</v>
+        <v>-3.567607079052599</v>
       </c>
       <c r="G20">
-        <v>-12.99894097425513</v>
+        <v>-15.65243922980163</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.18980496175531</v>
       </c>
       <c r="E21">
-        <v>-37.46918018931913</v>
+        <v>-40.96946643778494</v>
       </c>
       <c r="F21">
-        <v>-2.404184942638361</v>
+        <v>-3.346499251897355</v>
       </c>
       <c r="G21">
-        <v>-13.11694868054799</v>
+        <v>-15.43367672529382</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.94262866889901</v>
       </c>
       <c r="E22">
-        <v>-37.49799486942994</v>
+        <v>-41.33465163871149</v>
       </c>
       <c r="F22">
-        <v>-2.230607180320947</v>
+        <v>-3.248388245077184</v>
       </c>
       <c r="G22">
-        <v>-12.71938857728246</v>
+        <v>-15.42773760659636</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.69457221718965</v>
       </c>
       <c r="E23">
-        <v>-37.93997393257856</v>
+        <v>-41.81980290881224</v>
       </c>
       <c r="F23">
-        <v>-2.046764289148041</v>
+        <v>-3.134471159844196</v>
       </c>
       <c r="G23">
-        <v>-12.84867200168207</v>
+        <v>-15.21716208120717</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.432751385237131</v>
       </c>
       <c r="E24">
-        <v>-38.07529605711277</v>
+        <v>-41.98761683435148</v>
       </c>
       <c r="F24">
-        <v>-2.129529789831351</v>
+        <v>-2.933688983651443</v>
       </c>
       <c r="G24">
-        <v>-12.99619322145754</v>
+        <v>-15.24084075817681</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.171444572251474</v>
       </c>
       <c r="E25">
-        <v>-38.59075640374686</v>
+        <v>-41.91472878096103</v>
       </c>
       <c r="F25">
-        <v>-1.842039912485366</v>
+        <v>-2.884585020748295</v>
       </c>
       <c r="G25">
-        <v>-12.72515554761187</v>
+        <v>-15.47000665204178</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.919220403599251</v>
       </c>
       <c r="E26">
-        <v>-38.72100437315547</v>
+        <v>-42.04187248143738</v>
       </c>
       <c r="F26">
-        <v>-1.825006193581599</v>
+        <v>-2.959501740290079</v>
       </c>
       <c r="G26">
-        <v>-12.94534655251987</v>
+        <v>-15.50885093812682</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.680896524615284</v>
       </c>
       <c r="E27">
-        <v>-38.69881485051789</v>
+        <v>-41.8484115433557</v>
       </c>
       <c r="F27">
-        <v>-1.754869153953968</v>
+        <v>-2.73848420518174</v>
       </c>
       <c r="G27">
-        <v>-12.97482365000154</v>
+        <v>-15.57036087424648</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.484712620434826</v>
       </c>
       <c r="E28">
-        <v>-38.73507887037132</v>
+        <v>-42.00992183307626</v>
       </c>
       <c r="F28">
-        <v>-1.724515287213186</v>
+        <v>-2.807884826188283</v>
       </c>
       <c r="G28">
-        <v>-12.90007484227034</v>
+        <v>-15.7917171911843</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.343242659978169</v>
       </c>
       <c r="E29">
-        <v>-38.59127717825774</v>
+        <v>-42.24584853616488</v>
       </c>
       <c r="F29">
-        <v>-1.627790967425301</v>
+        <v>-2.848448321168569</v>
       </c>
       <c r="G29">
-        <v>-13.07400759435811</v>
+        <v>-15.39830851202501</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.267554264336654</v>
       </c>
       <c r="E30">
-        <v>-38.3147142136613</v>
+        <v>-42.44051857680661</v>
       </c>
       <c r="F30">
-        <v>-1.575569857985418</v>
+        <v>-2.557237417449208</v>
       </c>
       <c r="G30">
-        <v>-13.0824031378457</v>
+        <v>-15.79162284063644</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.278552324789429</v>
       </c>
       <c r="E31">
-        <v>-38.13118874755244</v>
+        <v>-41.68403246535127</v>
       </c>
       <c r="F31">
-        <v>-1.670067526194577</v>
+        <v>-2.673894742050657</v>
       </c>
       <c r="G31">
-        <v>-12.89249700353094</v>
+        <v>-16.05888483729457</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.374908652228576</v>
       </c>
       <c r="E32">
-        <v>-37.49906358929574</v>
+        <v>-41.45538301999299</v>
       </c>
       <c r="F32">
-        <v>-1.775720818217237</v>
+        <v>-2.882186068749787</v>
       </c>
       <c r="G32">
-        <v>-13.36206478282117</v>
+        <v>-15.73689952287228</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.559771131903224</v>
       </c>
       <c r="E33">
-        <v>-37.78385026269012</v>
+        <v>-41.24268286008971</v>
       </c>
       <c r="F33">
-        <v>-1.762518298551419</v>
+        <v>-2.841220815579143</v>
       </c>
       <c r="G33">
-        <v>-13.11343950227636</v>
+        <v>-16.10490804138152</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.83672316025674</v>
       </c>
       <c r="E34">
-        <v>-37.31915863815602</v>
+        <v>-40.96192426432516</v>
       </c>
       <c r="F34">
-        <v>-1.803466156006604</v>
+        <v>-2.636942928946577</v>
       </c>
       <c r="G34">
-        <v>-13.78340453469529</v>
+        <v>-15.95905202601231</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.185532714567698</v>
       </c>
       <c r="E35">
-        <v>-36.45999617128777</v>
+        <v>-40.43510424064283</v>
       </c>
       <c r="F35">
-        <v>-1.84758914571672</v>
+        <v>-2.862680501516067</v>
       </c>
       <c r="G35">
-        <v>-13.72409776663202</v>
+        <v>-16.15276528769722</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.602156469913139</v>
       </c>
       <c r="E36">
-        <v>-36.36382496878687</v>
+        <v>-40.36429475682189</v>
       </c>
       <c r="F36">
-        <v>-1.690915876988235</v>
+        <v>-2.71917081918547</v>
       </c>
       <c r="G36">
-        <v>-13.89208146838572</v>
+        <v>-16.20514142867403</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.076954002541816</v>
       </c>
       <c r="E37">
-        <v>-36.36111241285628</v>
+        <v>-39.84928725758857</v>
       </c>
       <c r="F37">
-        <v>-1.727143696982269</v>
+        <v>-2.672963657089911</v>
       </c>
       <c r="G37">
-        <v>-13.48343931392747</v>
+        <v>-16.0507276530858</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.583376957250698</v>
       </c>
       <c r="E38">
-        <v>-35.47329149823048</v>
+        <v>-39.37509715882338</v>
       </c>
       <c r="F38">
-        <v>-1.659524894259148</v>
+        <v>-2.785676296119228</v>
       </c>
       <c r="G38">
-        <v>-13.41741710423778</v>
+        <v>-16.40103468459655</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.119673049891961</v>
       </c>
       <c r="E39">
-        <v>-35.86760610821138</v>
+        <v>-38.88605366531304</v>
       </c>
       <c r="F39">
-        <v>-1.628075925811864</v>
+        <v>-2.836938984474072</v>
       </c>
       <c r="G39">
-        <v>-13.70352438137822</v>
+        <v>-16.33997001685193</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.672926195460677</v>
       </c>
       <c r="E40">
-        <v>-35.05823647729446</v>
+        <v>-38.47137450771965</v>
       </c>
       <c r="F40">
-        <v>-1.658839834417033</v>
+        <v>-2.902076826825809</v>
       </c>
       <c r="G40">
-        <v>-14.01960864837675</v>
+        <v>-16.05352175352095</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.221006766343471</v>
       </c>
       <c r="E41">
-        <v>-34.21213865793833</v>
+        <v>-37.76309626631296</v>
       </c>
       <c r="F41">
-        <v>-1.710900240580773</v>
+        <v>-2.656267083719084</v>
       </c>
       <c r="G41">
-        <v>-13.81627163080918</v>
+        <v>-16.3718240860308</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.766668066867457</v>
       </c>
       <c r="E42">
-        <v>-33.88086946309222</v>
+        <v>-38.01047095169297</v>
       </c>
       <c r="F42">
-        <v>-1.638483533860637</v>
+        <v>-2.68175760543803</v>
       </c>
       <c r="G42">
-        <v>-13.84136060017854</v>
+        <v>-16.3971398277696</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.29757369485144</v>
       </c>
       <c r="E43">
-        <v>-33.35973493852652</v>
+        <v>-37.32382749485793</v>
       </c>
       <c r="F43">
-        <v>-1.527903112526126</v>
+        <v>-2.567613547536675</v>
       </c>
       <c r="G43">
-        <v>-13.88193299103508</v>
+        <v>-16.42602764814528</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.8028925474135</v>
       </c>
       <c r="E44">
-        <v>-33.10176815244258</v>
+        <v>-36.57789499207747</v>
       </c>
       <c r="F44">
-        <v>-1.573358945387346</v>
+        <v>-2.433015441725395</v>
       </c>
       <c r="G44">
-        <v>-13.93926667395695</v>
+        <v>-16.19015789956329</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.29154678048368</v>
       </c>
       <c r="E45">
-        <v>-32.31161736521422</v>
+        <v>-36.17611972116894</v>
       </c>
       <c r="F45">
-        <v>-1.431071104975878</v>
+        <v>-2.573929020615618</v>
       </c>
       <c r="G45">
-        <v>-13.89806031362964</v>
+        <v>-16.31705442062909</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.75259523366774</v>
       </c>
       <c r="E46">
-        <v>-31.80781331067587</v>
+        <v>-35.70708302582448</v>
       </c>
       <c r="F46">
-        <v>-1.457972336381792</v>
+        <v>-2.473610414666987</v>
       </c>
       <c r="G46">
-        <v>-13.74493434025619</v>
+        <v>-16.52461900485032</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.18638782159359</v>
       </c>
       <c r="E47">
-        <v>-31.58780872219823</v>
+        <v>-35.31229971878379</v>
       </c>
       <c r="F47">
-        <v>-1.453036923395912</v>
+        <v>-2.450051645731369</v>
       </c>
       <c r="G47">
-        <v>-13.54697199337162</v>
+        <v>-16.33897685319015</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.60216236884799</v>
       </c>
       <c r="E48">
-        <v>-31.28562591590338</v>
+        <v>-34.8878164149638</v>
       </c>
       <c r="F48">
-        <v>-1.456463879341294</v>
+        <v>-2.465578564329443</v>
       </c>
       <c r="G48">
-        <v>-13.80445463850675</v>
+        <v>-16.42153192730295</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.98401028446821</v>
       </c>
       <c r="E49">
-        <v>-30.76242867142719</v>
+        <v>-34.84907531982818</v>
       </c>
       <c r="F49">
-        <v>-1.329560478334618</v>
+        <v>-2.261871422837405</v>
       </c>
       <c r="G49">
-        <v>-13.69793949105347</v>
+        <v>-16.55706235113518</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.33866210924713</v>
       </c>
       <c r="E50">
-        <v>-30.27048016184093</v>
+        <v>-34.20235941831877</v>
       </c>
       <c r="F50">
-        <v>-1.470017626785899</v>
+        <v>-2.333064630903606</v>
       </c>
       <c r="G50">
-        <v>-13.76283280471426</v>
+        <v>-16.51765030649015</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.66904258965406</v>
       </c>
       <c r="E51">
-        <v>-29.65366350996716</v>
+        <v>-33.50692845767184</v>
       </c>
       <c r="F51">
-        <v>-1.200278834514505</v>
+        <v>-2.317212992283635</v>
       </c>
       <c r="G51">
-        <v>-13.94139701001147</v>
+        <v>-16.38442402235326</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.95458782697645</v>
       </c>
       <c r="E52">
-        <v>-29.22691370490633</v>
+        <v>-33.07772874817286</v>
       </c>
       <c r="F52">
-        <v>-1.370501708850581</v>
+        <v>-2.325064258527369</v>
       </c>
       <c r="G52">
-        <v>-13.84440630207467</v>
+        <v>-16.61910694035943</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.20672120596741</v>
       </c>
       <c r="E53">
-        <v>-28.83125187390815</v>
+        <v>-32.98184057529745</v>
       </c>
       <c r="F53">
-        <v>-1.273731828855542</v>
+        <v>-2.29001851881713</v>
       </c>
       <c r="G53">
-        <v>-14.11935869602053</v>
+        <v>-16.88974900401315</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.42195172325457</v>
       </c>
       <c r="E54">
-        <v>-28.30027018261277</v>
+        <v>-32.22821872365196</v>
       </c>
       <c r="F54">
-        <v>-1.335931452029549</v>
+        <v>-2.289046843853646</v>
       </c>
       <c r="G54">
-        <v>-13.71408502164849</v>
+        <v>-16.81584273012169</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.58199303652162</v>
       </c>
       <c r="E55">
-        <v>-28.01883457998407</v>
+        <v>-32.34611980867866</v>
       </c>
       <c r="F55">
-        <v>-1.345979548625507</v>
+        <v>-2.311734998648922</v>
       </c>
       <c r="G55">
-        <v>-14.05106710736368</v>
+        <v>-16.90069366756599</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.70255550804456</v>
       </c>
       <c r="E56">
-        <v>-27.6812096718682</v>
+        <v>-31.72153229540773</v>
       </c>
       <c r="F56">
-        <v>-1.183171390911889</v>
+        <v>-2.179641047496304</v>
       </c>
       <c r="G56">
-        <v>-13.92675612236404</v>
+        <v>-16.81301055841285</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.77775598626973</v>
       </c>
       <c r="E57">
-        <v>-27.13968569308297</v>
+        <v>-31.67836688116661</v>
       </c>
       <c r="F57">
-        <v>-1.171597441559975</v>
+        <v>-2.262403234710002</v>
       </c>
       <c r="G57">
-        <v>-14.13437864113221</v>
+        <v>-16.70564294548321</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.79991200398347</v>
       </c>
       <c r="E58">
-        <v>-27.2262565306876</v>
+        <v>-30.99645567966959</v>
       </c>
       <c r="F58">
-        <v>-1.375050274259353</v>
+        <v>-2.412320338901254</v>
       </c>
       <c r="G58">
-        <v>-13.98571031732738</v>
+        <v>-16.78686055919815</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.78892222995462</v>
       </c>
       <c r="E59">
-        <v>-26.60474611550488</v>
+        <v>-31.16453904941229</v>
       </c>
       <c r="F59">
-        <v>-1.328018058230605</v>
+        <v>-2.296256953727613</v>
       </c>
       <c r="G59">
-        <v>-14.03869725395619</v>
+        <v>-16.4700247983622</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.73766784990816</v>
       </c>
       <c r="E60">
-        <v>-26.54628804453987</v>
+        <v>-30.75046897157294</v>
       </c>
       <c r="F60">
-        <v>-1.485158526174269</v>
+        <v>-2.363223002937328</v>
       </c>
       <c r="G60">
-        <v>-14.00532861019311</v>
+        <v>-17.01217628860094</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.65036899833326</v>
       </c>
       <c r="E61">
-        <v>-26.31017793825394</v>
+        <v>-30.8562450674441</v>
       </c>
       <c r="F61">
-        <v>-1.326673617935862</v>
+        <v>-2.377709492077485</v>
       </c>
       <c r="G61">
-        <v>-13.97797853822042</v>
+        <v>-16.83931780854067</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.54456921630425</v>
       </c>
       <c r="E62">
-        <v>-26.16684267896316</v>
+        <v>-30.61718239610517</v>
       </c>
       <c r="F62">
-        <v>-1.491565948034923</v>
+        <v>-2.315145387246247</v>
       </c>
       <c r="G62">
-        <v>-14.10345483524987</v>
+        <v>-17.04708599131256</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.40948649927142</v>
       </c>
       <c r="E63">
-        <v>-26.15266855531915</v>
+        <v>-30.47310899555114</v>
       </c>
       <c r="F63">
-        <v>-1.523201299147836</v>
+        <v>-2.539034872140092</v>
       </c>
       <c r="G63">
-        <v>-14.21352550861233</v>
+        <v>-16.71732420541852</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.2580674146058</v>
       </c>
       <c r="E64">
-        <v>-26.32664346974583</v>
+        <v>-30.43479357697224</v>
       </c>
       <c r="F64">
-        <v>-1.486945314662107</v>
+        <v>-2.373772261811979</v>
       </c>
       <c r="G64">
-        <v>-14.20631845097334</v>
+        <v>-16.96793746855966</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.09995027966744</v>
       </c>
       <c r="E65">
-        <v>-25.65666479725902</v>
+        <v>-30.16392290420344</v>
       </c>
       <c r="F65">
-        <v>-1.709575681103697</v>
+        <v>-2.601725717183959</v>
       </c>
       <c r="G65">
-        <v>-13.92840642931537</v>
+        <v>-17.0500108582965</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.91750587050502</v>
       </c>
       <c r="E66">
-        <v>-25.69013927712372</v>
+        <v>-30.3020504183854</v>
       </c>
       <c r="F66">
-        <v>-1.477973267322386</v>
+        <v>-2.608904349096619</v>
       </c>
       <c r="G66">
-        <v>-14.06789295506702</v>
+        <v>-16.86797720127414</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.72456550145479</v>
       </c>
       <c r="E67">
-        <v>-25.52899805803477</v>
+        <v>-29.76635005717403</v>
       </c>
       <c r="F67">
-        <v>-1.74939861562588</v>
+        <v>-2.708202406405002</v>
       </c>
       <c r="G67">
-        <v>-14.05089495899563</v>
+        <v>-16.76086781089656</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.51873793847796</v>
       </c>
       <c r="E68">
-        <v>-25.62828032217894</v>
+        <v>-30.10087975330566</v>
       </c>
       <c r="F68">
-        <v>-1.68294284073629</v>
+        <v>-2.829929339511583</v>
       </c>
       <c r="G68">
-        <v>-13.97374600574846</v>
+        <v>-16.50593594109944</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.27997415414732</v>
       </c>
       <c r="E69">
-        <v>-25.21081388883383</v>
+        <v>-30.02329567236924</v>
       </c>
       <c r="F69">
-        <v>-1.919316650757726</v>
+        <v>-2.790470886646632</v>
       </c>
       <c r="G69">
-        <v>-13.86973032017733</v>
+        <v>-16.74005937690947</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.02047557589888</v>
       </c>
       <c r="E70">
-        <v>-25.24607711593156</v>
+        <v>-30.04472441137354</v>
       </c>
       <c r="F70">
-        <v>-1.840896765469502</v>
+        <v>-2.967593233080625</v>
       </c>
       <c r="G70">
-        <v>-13.92225378043064</v>
+        <v>-16.81005589651905</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.73035142044809</v>
       </c>
       <c r="E71">
-        <v>-25.05819525782733</v>
+        <v>-29.86793052187708</v>
       </c>
       <c r="F71">
-        <v>-2.145483317641867</v>
+        <v>-2.989984832345698</v>
       </c>
       <c r="G71">
-        <v>-14.17342321522237</v>
+        <v>-16.75404643181289</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.39572351380406</v>
       </c>
       <c r="E72">
-        <v>-25.75668520266643</v>
+        <v>-30.20973294726503</v>
       </c>
       <c r="F72">
-        <v>-2.281755553974205</v>
+        <v>-3.061234369395289</v>
       </c>
       <c r="G72">
-        <v>-13.53956961354581</v>
+        <v>-16.25862825767927</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.03043625053106</v>
       </c>
       <c r="E73">
-        <v>-25.2632219185246</v>
+        <v>-29.62749119443983</v>
       </c>
       <c r="F73">
-        <v>-2.163909522149739</v>
+        <v>-3.244806384427479</v>
       </c>
       <c r="G73">
-        <v>-13.77696883416695</v>
+        <v>-16.59090936872868</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.62537706215822</v>
       </c>
       <c r="E74">
-        <v>-25.43087508323657</v>
+        <v>-30.0501948079748</v>
       </c>
       <c r="F74">
-        <v>-2.297638670555482</v>
+        <v>-3.234514747815098</v>
       </c>
       <c r="G74">
-        <v>-13.71150279612786</v>
+        <v>-16.20767399601157</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.18169588165709</v>
       </c>
       <c r="E75">
-        <v>-25.69848978319386</v>
+        <v>-30.33488638341502</v>
       </c>
       <c r="F75">
-        <v>-2.446854147556563</v>
+        <v>-3.19008029196153</v>
       </c>
       <c r="G75">
-        <v>-13.76391866365114</v>
+        <v>-16.43641779532028</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.71579133953581</v>
       </c>
       <c r="E76">
-        <v>-25.63210235424141</v>
+        <v>-30.03373833343093</v>
       </c>
       <c r="F76">
-        <v>-2.65212027650067</v>
+        <v>-3.400980975979478</v>
       </c>
       <c r="G76">
-        <v>-13.32614205317454</v>
+        <v>-16.34439621623793</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.22416928355604</v>
       </c>
       <c r="E77">
-        <v>-25.80681993840535</v>
+        <v>-30.32274780883746</v>
       </c>
       <c r="F77">
-        <v>-2.720289943546652</v>
+        <v>-3.490351878332711</v>
       </c>
       <c r="G77">
-        <v>-13.55680927944157</v>
+        <v>-16.23019894786077</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.721267153337617</v>
       </c>
       <c r="E78">
-        <v>-26.42977946527052</v>
+        <v>-30.67056631194459</v>
       </c>
       <c r="F78">
-        <v>-2.675524140731964</v>
+        <v>-3.532123132986279</v>
       </c>
       <c r="G78">
-        <v>-13.04235546845713</v>
+        <v>-16.13382234612151</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.222100468727078</v>
       </c>
       <c r="E79">
-        <v>-25.89785585138155</v>
+        <v>-30.71243884685652</v>
       </c>
       <c r="F79">
-        <v>-2.606270969123119</v>
+        <v>-3.721288284722172</v>
       </c>
       <c r="G79">
-        <v>-13.45936502676589</v>
+        <v>-15.99085974755362</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.722537759186469</v>
       </c>
       <c r="E80">
-        <v>-26.79966069374303</v>
+        <v>-31.01238005851756</v>
       </c>
       <c r="F80">
-        <v>-2.822298418996994</v>
+        <v>-3.681621911639117</v>
       </c>
       <c r="G80">
-        <v>-12.81721188742238</v>
+        <v>-16.06100689698524</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.240772636508067</v>
       </c>
       <c r="E81">
-        <v>-26.68619524900684</v>
+        <v>-31.37453797456999</v>
       </c>
       <c r="F81">
-        <v>-2.874101202898464</v>
+        <v>-3.740541199898038</v>
       </c>
       <c r="G81">
-        <v>-12.8718060939105</v>
+        <v>-15.65302850690762</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.784452664540535</v>
       </c>
       <c r="E82">
-        <v>-27.35563503308674</v>
+        <v>-31.5878517427013</v>
       </c>
       <c r="F82">
-        <v>-2.703458346289169</v>
+        <v>-3.687970519414173</v>
       </c>
       <c r="G82">
-        <v>-12.65799782080221</v>
+        <v>-16.14947129488565</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.347581195423993</v>
       </c>
       <c r="E83">
-        <v>-27.52660756924634</v>
+        <v>-31.88944131890113</v>
       </c>
       <c r="F83">
-        <v>-2.804755254140506</v>
+        <v>-3.88427122795778</v>
       </c>
       <c r="G83">
-        <v>-12.61493424442737</v>
+        <v>-15.91134706479141</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.94817046167245</v>
       </c>
       <c r="E84">
-        <v>-28.37719989905507</v>
+        <v>-32.54130835959427</v>
       </c>
       <c r="F84">
-        <v>-3.085312524692462</v>
+        <v>-3.840766200330153</v>
       </c>
       <c r="G84">
-        <v>-12.67581517689457</v>
+        <v>-15.89867926228539</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.588930678008775</v>
       </c>
       <c r="E85">
-        <v>-29.19645971720474</v>
+        <v>-33.39016175538406</v>
       </c>
       <c r="F85">
-        <v>-2.994014011392915</v>
+        <v>-3.832182657302344</v>
       </c>
       <c r="G85">
-        <v>-12.69929025531354</v>
+        <v>-15.57619571075944</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.267671764429132</v>
       </c>
       <c r="E86">
-        <v>-29.39583484234045</v>
+        <v>-33.53293548389789</v>
       </c>
       <c r="F86">
-        <v>-3.074969529301108</v>
+        <v>-4.056478042223561</v>
       </c>
       <c r="G86">
-        <v>-12.28974597719584</v>
+        <v>-15.70298463909522</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.004815197650318</v>
       </c>
       <c r="E87">
-        <v>-30.880979592474</v>
+        <v>-34.66564495167349</v>
       </c>
       <c r="F87">
-        <v>-2.98876630389618</v>
+        <v>-4.111436905929697</v>
       </c>
       <c r="G87">
-        <v>-12.87676529112833</v>
+        <v>-15.70924157016444</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.802266931668716</v>
       </c>
       <c r="E88">
-        <v>-31.36570292178102</v>
+        <v>-35.03374648986097</v>
       </c>
       <c r="F88">
-        <v>-3.170756137189023</v>
+        <v>-4.051709959453047</v>
       </c>
       <c r="G88">
-        <v>-12.34751830740166</v>
+        <v>-15.39863791130617</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.666765418154498</v>
       </c>
       <c r="E89">
-        <v>-32.6893939881191</v>
+        <v>-35.70541654738965</v>
       </c>
       <c r="F89">
-        <v>-3.166806481412475</v>
+        <v>-4.256342387334011</v>
       </c>
       <c r="G89">
-        <v>-12.58981382487538</v>
+        <v>-15.4771524645883</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.614637954909568</v>
       </c>
       <c r="E90">
-        <v>-33.25186442342682</v>
+        <v>-36.88772186249725</v>
       </c>
       <c r="F90">
-        <v>-3.283227721304126</v>
+        <v>-4.357693967433934</v>
       </c>
       <c r="G90">
-        <v>-12.55191138899627</v>
+        <v>-15.79959960011331</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.640322788005185</v>
       </c>
       <c r="E91">
-        <v>-34.23456139698731</v>
+        <v>-37.74795078499431</v>
       </c>
       <c r="F91">
-        <v>-3.364300867383516</v>
+        <v>-4.291895087894764</v>
       </c>
       <c r="G91">
-        <v>-12.66863129307435</v>
+        <v>-15.57665422131663</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.748828837101716</v>
       </c>
       <c r="E92">
-        <v>-35.40173255196127</v>
+        <v>-38.86807562350258</v>
       </c>
       <c r="F92">
-        <v>-3.68326207909666</v>
+        <v>-4.385298482764824</v>
       </c>
       <c r="G92">
-        <v>-12.61461312151006</v>
+        <v>-16.06859632263402</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.943591028584606</v>
       </c>
       <c r="E93">
-        <v>-36.52015015576865</v>
+        <v>-39.72444855038211</v>
       </c>
       <c r="F93">
-        <v>-3.756020901554152</v>
+        <v>-4.604587215103521</v>
       </c>
       <c r="G93">
-        <v>-12.75142472646598</v>
+        <v>-16.16866583792234</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.205959494779172</v>
       </c>
       <c r="E94">
-        <v>-38.02846937163645</v>
+        <v>-40.68259440211003</v>
       </c>
       <c r="F94">
-        <v>-3.678308442027919</v>
+        <v>-4.69450732504481</v>
       </c>
       <c r="G94">
-        <v>-13.24443447871979</v>
+        <v>-16.07787081596229</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.534556687057152</v>
       </c>
       <c r="E95">
-        <v>-39.40532925129859</v>
+        <v>-42.03623905977184</v>
       </c>
       <c r="F95">
-        <v>-3.75654111628311</v>
+        <v>-4.747513726782548</v>
       </c>
       <c r="G95">
-        <v>-13.12057703845903</v>
+        <v>-16.03599903598159</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.917265866753518</v>
       </c>
       <c r="E96">
-        <v>-40.81569531014348</v>
+        <v>-43.55650891854589</v>
       </c>
       <c r="F96">
-        <v>-4.00637341149783</v>
+        <v>-5.024233171157333</v>
       </c>
       <c r="G96">
-        <v>-13.16234950207356</v>
+        <v>-16.22355137241792</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.323908509108337</v>
       </c>
       <c r="E97">
-        <v>-42.26796107474433</v>
+        <v>-44.89603153001477</v>
       </c>
       <c r="F97">
-        <v>-4.079030344764777</v>
+        <v>-5.24634166613516</v>
       </c>
       <c r="G97">
-        <v>-13.79950371765277</v>
+        <v>-16.93585828228412</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.746934696780797</v>
       </c>
       <c r="E98">
-        <v>-43.7461455603281</v>
+        <v>-46.22570244627998</v>
       </c>
       <c r="F98">
-        <v>-4.229239034281814</v>
+        <v>-5.218329594042092</v>
       </c>
       <c r="G98">
-        <v>-13.89010838324431</v>
+        <v>-16.78656426537238</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.15579966298823</v>
       </c>
       <c r="E99">
-        <v>-45.22017290677281</v>
+        <v>-47.69421411138335</v>
       </c>
       <c r="F99">
-        <v>-4.350391080410853</v>
+        <v>-5.335123599265002</v>
       </c>
       <c r="G99">
-        <v>-13.97952125244172</v>
+        <v>-17.21613899927544</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.527729872504358</v>
       </c>
       <c r="E100">
-        <v>-47.23434304743042</v>
+        <v>-49.09779878040175</v>
       </c>
       <c r="F100">
-        <v>-4.503359061746615</v>
+        <v>-5.679173574506735</v>
       </c>
       <c r="G100">
-        <v>-14.37229596213024</v>
+        <v>-17.54267134799591</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.834897766704916</v>
       </c>
       <c r="E101">
-        <v>-48.79786775780723</v>
+        <v>-50.50192913053808</v>
       </c>
       <c r="F101">
-        <v>-4.717752142734767</v>
+        <v>-5.734969089289698</v>
       </c>
       <c r="G101">
-        <v>-14.77607326991853</v>
+        <v>-17.44155073449888</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.072229727141895</v>
       </c>
       <c r="E102">
-        <v>-50.92051749331858</v>
+        <v>-52.49299160045305</v>
       </c>
       <c r="F102">
-        <v>-4.793423504980502</v>
+        <v>-5.77330013411944</v>
       </c>
       <c r="G102">
-        <v>-14.74949621032926</v>
+        <v>-17.57394938225095</v>
       </c>
     </row>
   </sheetData>
